--- a/Apex 데이터 테이블.xlsx
+++ b/Apex 데이터 테이블.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\{ 프로젝트 기반 풀스택 개발자 양성 과정 }\A조 Apex\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5B6964-8CAA-4D47-9223-EEC3EEAFCA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FFADFB-C306-4CF3-9031-1A7E979B6422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AC449A03-C93A-4853-895D-61D8656DAC6C}"/>
+    <workbookView xWindow="7200" yWindow="4215" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{AC449A03-C93A-4853-895D-61D8656DAC6C}"/>
   </bookViews>
   <sheets>
     <sheet name="관리자" sheetId="1" r:id="rId1"/>
@@ -316,10 +316,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>대여가능여부(1:가능, 0:불가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>pd_rent_length</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -440,6 +436,10 @@
   </si>
   <si>
     <t>따로 받을지 고민</t>
+  </si>
+  <si>
+    <t>대여가능여부(0:불가 1:대여중 2:입고 대기중) - 사전 예약</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -485,7 +485,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -499,16 +499,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1249,14 +1246,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1438,7 +1435,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.25" customWidth="1"/>
-    <col min="2" max="2" width="13" style="6" customWidth="1"/>
+    <col min="2" max="2" width="13" style="5" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
     <col min="5" max="5" width="15.125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41.375" style="1" customWidth="1"/>
@@ -1446,20 +1443,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1476,10 +1473,10 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1488,211 +1485,211 @@
       <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="1"/>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>68</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="1">
         <v>0</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="1">
         <v>3</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>72</v>
+      <c r="F15" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="5"/>
+      <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" s="5"/>
+        <v>77</v>
+      </c>
+      <c r="F20" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1718,14 +1715,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="A1" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1749,7 +1746,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>7</v>
@@ -1758,12 +1755,12 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>10</v>
@@ -1772,12 +1769,12 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>14</v>
@@ -1791,21 +1788,21 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
@@ -1819,57 +1816,57 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="F10" t="s">
         <v>99</v>
-      </c>
-      <c r="F10" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>35</v>
@@ -1880,7 +1877,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>35</v>
@@ -1895,13 +1892,13 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>103</v>
+      <c r="A16" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Apex 데이터 테이블.xlsx
+++ b/Apex 데이터 테이블.xlsx
@@ -2,25 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\{ 프로젝트 기반 풀스택 개발자 양성 과정 }\A조 Apex\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FFADFB-C306-4CF3-9031-1A7E979B6422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1C53E1-544D-47CD-A92E-E45A42454F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4215" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{AC449A03-C93A-4853-895D-61D8656DAC6C}"/>
+    <workbookView xWindow="7275" yWindow="3225" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{AC449A03-C93A-4853-895D-61D8656DAC6C}"/>
   </bookViews>
   <sheets>
     <sheet name="관리자" sheetId="1" r:id="rId1"/>
-    <sheet name="게임기 대여" sheetId="4" r:id="rId2"/>
+    <sheet name="게임기(자산)" sheetId="4" r:id="rId2"/>
     <sheet name="사용자" sheetId="5" r:id="rId3"/>
+    <sheet name="우편번호" sheetId="7" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'게임기 대여'!$A$2:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'게임기(자산)'!$A$2:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">관리자!$A$2:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">사용자!$A$2:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">우편번호!$A$2:$F$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="130">
   <si>
     <t>Column</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -387,10 +389,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>user_postcode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>우편번호 (검색하기)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -403,10 +401,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>varchar(300)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>주소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -423,10 +417,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>char(5)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>char(13)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -439,6 +429,110 @@
   </si>
   <si>
     <t>대여가능여부(0:불가 1:대여중 2:입고 대기중) - 사전 예약</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_nickname</t>
+  </si>
+  <si>
+    <t>별명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_zipcode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(200)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_grade</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>등급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_state</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원여부(상태)(0:비회원, 1:회원, 2:휴면회원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unique (user_nickname)</t>
+  </si>
+  <si>
+    <t>우편번호 테이블(tbl_address)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zipcode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>area1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>area2</t>
+  </si>
+  <si>
+    <t>area3</t>
+  </si>
+  <si>
+    <t>area4</t>
+  </si>
+  <si>
+    <t>char(7)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>char(15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>char(30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>char(40)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우편번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시/도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구/군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동/면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>번지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>) comment '우편번호 테이블';</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -446,7 +540,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -459,6 +553,14 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -485,7 +587,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -505,6 +607,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -805,13 +916,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>361949</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>95249</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>638174</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>191338</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -850,13 +961,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>371474</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>47624</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>647699</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>143713</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -895,13 +1006,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>311425</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>196424</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>85724</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1236,6 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDA1C81-F5F9-4FD6-90F8-0C9B4A5AB8FF}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1431,6 +1543,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5DC1406-7C3A-4C97-B258-3F38FE783439}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1630,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1705,7 +1818,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{140538D2-E239-434C-A085-2440FB464E56}">
-  <dimension ref="A1:F17"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1772,133 +1886,180 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>101</v>
+    <row r="6" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F6" t="s">
-        <v>93</v>
+      <c r="F6" s="7" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>103</v>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1910,4 +2071,121 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D763ACB1-241E-41CA-9176-41B60B15EF02}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="13" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="25.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="F3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8" s="1"/>
+      <c r="F8"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:F2" xr:uid="{1CDA1C81-F5F9-4FD6-90F8-0C9B4A5AB8FF}"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Apex 데이터 테이블.xlsx
+++ b/Apex 데이터 테이블.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\{ 프로젝트 기반 풀스택 개발자 양성 과정 }\A조 Apex\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC7F6A6-8B5A-4D9D-B908-99E23A4DB33E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8BAB108-7E0A-4C93-BBFD-12CCEDA280A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2505" yWindow="1305" windowWidth="18840" windowHeight="12255" activeTab="4" xr2:uid="{AC449A03-C93A-4853-895D-61D8656DAC6C}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="2" activeTab="5" xr2:uid="{AC449A03-C93A-4853-895D-61D8656DAC6C}"/>
   </bookViews>
   <sheets>
     <sheet name="관리자" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="사용자" sheetId="5" r:id="rId3"/>
     <sheet name="우편번호" sheetId="7" r:id="rId4"/>
     <sheet name="기기 대여 이력" sheetId="9" r:id="rId5"/>
+    <sheet name="희망 기기 요청" sheetId="10" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'게임기(자산)'!$A$2:$G$2</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="166">
   <si>
     <t>Column</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -209,22 +210,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게임기 테이블(tbl_product)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GTIN(Global Trade Item Number) 유통표준코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pd_gtin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pd_no</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -233,78 +218,29 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>제품번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pd_name</t>
-  </si>
-  <si>
-    <t>pd_regdate</t>
-  </si>
-  <si>
-    <t>pd_moddate</t>
-  </si>
-  <si>
     <t>varchar(50)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>제품이름</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pd_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>varchar(20)</t>
   </si>
   <si>
-    <t>제품유형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pd_rental_price</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>대여가격</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pd_thumbnail</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제품사진</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>제조사</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pd_year</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>char(10)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>제조연도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>text</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>제품상세설명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>varchar(30)</t>
   </si>
   <si>
@@ -312,23 +248,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pd_rent_length</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>대여기간(최소 3일)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pd_content</t>
-  </si>
-  <si>
-    <t>pd_call_number</t>
-  </si>
-  <si>
-    <t>pd_rent_able</t>
-  </si>
-  <si>
     <t>foreign key (staff_id) references tbl_staff (staff_id)</t>
   </si>
   <si>
@@ -528,22 +451,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pd_manufac_com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>primary key (pd_no),</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>사용자 아이디</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>제품 번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>FK</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -576,42 +487,171 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>foreign key (pd_no) references tbl_product (pd_no),
+    <t>&gt;&gt; AddressDTO.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;&gt;RentalVO // RentalDTO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기기 대여 이력 테이블(tbl_rental)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rt_no</t>
+  </si>
+  <si>
+    <t>rt_start_date</t>
+  </si>
+  <si>
+    <t>rt_end_date</t>
+  </si>
+  <si>
+    <t>rt_expire_date</t>
+  </si>
+  <si>
+    <t>rt_regdate</t>
+  </si>
+  <si>
+    <t>rt_moddate</t>
+  </si>
+  <si>
+    <t>primary key (rt_no),</t>
+  </si>
+  <si>
+    <t>gds_no</t>
+  </si>
+  <si>
+    <t>gds_type</t>
+  </si>
+  <si>
+    <t>gds_name</t>
+  </si>
+  <si>
+    <t>gds_thumbnail</t>
+  </si>
+  <si>
+    <t>gds_rental_price</t>
+  </si>
+  <si>
+    <t>gds_manufac_com</t>
+  </si>
+  <si>
+    <t>gds_year</t>
+  </si>
+  <si>
+    <t>gds_content</t>
+  </si>
+  <si>
+    <t>gds_call_number</t>
+  </si>
+  <si>
+    <t>gds_rent_able</t>
+  </si>
+  <si>
+    <t>gds_rent_length</t>
+  </si>
+  <si>
+    <t>gds_regdate</t>
+  </si>
+  <si>
+    <t>gds_moddate</t>
+  </si>
+  <si>
+    <t>primary key (gds_no),</t>
+  </si>
+  <si>
+    <t>상품번호</t>
+  </si>
+  <si>
+    <t>상품유형</t>
+  </si>
+  <si>
+    <t>상품이름</t>
+  </si>
+  <si>
+    <t>상품사진</t>
+  </si>
+  <si>
+    <t>상품상세설명</t>
+  </si>
+  <si>
+    <t>게임기 테이블(tbl_goods)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gds_no</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foreign key (gds_no) references tbl_product (gds_no),
 foreign key (mb_id) references tbl_member (mb_id)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;&gt; AddressDTO.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;&gt;RentalVO // RentalDTO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기기 대여 이력 테이블(tbl_rental)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rt_no</t>
-  </si>
-  <si>
-    <t>rt_start_date</t>
-  </si>
-  <si>
-    <t>rt_end_date</t>
-  </si>
-  <si>
-    <t>rt_expire_date</t>
-  </si>
-  <si>
-    <t>rt_regdate</t>
-  </si>
-  <si>
-    <t>rt_moddate</t>
-  </si>
-  <si>
-    <t>primary key (rt_no),</t>
+  </si>
+  <si>
+    <t>상품 번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wgd_no</t>
+  </si>
+  <si>
+    <t>wgd_regdate</t>
+  </si>
+  <si>
+    <t>wgd_moddate</t>
+  </si>
+  <si>
+    <t>primary key (wgd_no),</t>
+  </si>
+  <si>
+    <t>요청 번호(자동증가)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wgd_name</t>
+  </si>
+  <si>
+    <t>wgd_manufac_com</t>
+  </si>
+  <si>
+    <t>wgd_year</t>
+  </si>
+  <si>
+    <t>출시연도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고여부(0:미입고 1:입고완료 2:입고 대기중) - 사전 예약</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foreign key (mb_id) references tbl_member (mb_id)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>) comment '희망 기기 요청 테이블';</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>희망 기기 요청 테이블(tbl_wish_goods)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wgd_result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wgd_specific</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품 사양</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품 이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -665,7 +705,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -701,9 +741,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -773,13 +810,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>400049</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>110374</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>13125</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -818,13 +855,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>165880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>36813</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1126,6 +1163,51 @@
         <a:xfrm>
           <a:off x="3664225" y="2711024"/>
           <a:ext cx="2403199" cy="4718476"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>129309</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>74913</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF5C0830-C905-41C1-B648-1E2D252FEBE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:srcRect l="4375" t="4168" r="1563" b="2037"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4400550"/>
+          <a:ext cx="6111009" cy="3427713"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1490,7 +1572,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -1631,7 +1713,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5DC1406-7C3A-4C97-B258-3F38FE783439}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.25" customWidth="1"/>
@@ -1644,7 +1726,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -1667,7 +1749,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>4</v>
@@ -1678,20 +1760,18 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1714,194 +1794,178 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>47</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>48</v>
+      <c r="A7" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G7" s="4" t="s">
-        <v>52</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>58</v>
+      <c r="A8" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+        <v>41</v>
+      </c>
       <c r="G8" s="4" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>56</v>
+      <c r="A9" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>45</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
       <c r="G9" s="4" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>128</v>
+      <c r="A10" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+        <v>47</v>
+      </c>
       <c r="G10" s="4" t="s">
-        <v>60</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>63</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>64</v>
+        <v>49</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>71</v>
+      <c r="A13" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>72</v>
+      <c r="A14" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>68</v>
+      <c r="A15" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="1">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>37</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="G18" s="4"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>73</v>
+      <c r="A19" t="s">
+        <v>53</v>
       </c>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" s="4"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>75</v>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1929,7 +1993,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -1959,7 +2023,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>7</v>
@@ -1968,12 +2032,12 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -1982,12 +2046,12 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>13</v>
@@ -2001,35 +2065,35 @@
     </row>
     <row r="6" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>23</v>
@@ -2038,90 +2102,90 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>34</v>
@@ -2132,7 +2196,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>34</v>
@@ -2143,7 +2207,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
@@ -2153,12 +2217,12 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2187,7 +2251,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -2195,7 +2259,7 @@
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
       <c r="G1" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -2220,63 +2284,63 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D3" s="1"/>
       <c r="F3" s="4" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C8"/>
       <c r="D8"/>
@@ -2308,7 +2372,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -2317,7 +2381,7 @@
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -2334,7 +2398,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>4</v>
@@ -2345,7 +2409,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>31</v>
@@ -2355,15 +2419,15 @@
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>31</v>
@@ -2375,12 +2439,12 @@
         <v>11</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>7</v>
@@ -2392,55 +2456,55 @@
         <v>11</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="C6" s="9"/>
       <c r="F6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="C7" s="9"/>
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="G8" s="4" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>34</v>
@@ -2451,7 +2515,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>34</v>
@@ -2462,18 +2526,18 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
-      <c r="F12" s="12"/>
+      <c r="F12"/>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -2485,7 +2549,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -2497,4 +2561,290 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E39C24-38AC-4CC0-AEBE-2170671EC494}">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.25" customWidth="1"/>
+    <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" customWidth="1"/>
+    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="F7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="5"/>
+      <c r="C15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A13:D13"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>